--- a/Gold_ETF_Daily_Price_Tracker.xlsx
+++ b/Gold_ETF_Daily_Price_Tracker.xlsx
@@ -22,13 +22,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="dd\-mmm\-yy"/>
     <numFmt numFmtId="167" formatCode="[$₹-4009]#,##0.00"/>
     <numFmt numFmtId="168" formatCode="[$₹-4009]#,##0.00;[Red]\([$₹-4009]#,##0.00\)"/>
     <numFmt numFmtId="169" formatCode="0.00%;[Red]\(0.00%\)"/>
+    <numFmt numFmtId="170" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="171" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="172" formatCode="dd-mmm-yy"/>
+    <numFmt numFmtId="173" formatCode="[$₹-en-IN]#,##0.00"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -180,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -251,6 +255,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1711,7 +1722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="33" min="1" max="11"/>
@@ -2119,6 +2130,44 @@
         <v>100897.45</v>
       </c>
       <c r="L10" s="13" t="n">
+        <v>161432.684648998</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>301332.4</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>129.83</v>
+      </c>
+      <c r="E11" s="36" t="n">
+        <v>251091.22</v>
+      </c>
+      <c r="F11" s="36" t="n">
+        <v>130.01</v>
+      </c>
+      <c r="G11" s="36" t="n">
+        <v>200735.44</v>
+      </c>
+      <c r="H11" s="36" t="n">
+        <v>133.72</v>
+      </c>
+      <c r="I11" s="36" t="n">
+        <v>148562.92</v>
+      </c>
+      <c r="J11" s="36" t="n">
+        <v>136.45</v>
+      </c>
+      <c r="K11" s="36" t="n">
+        <v>100017.85</v>
+      </c>
+      <c r="L11" s="36" t="n">
         <v>161432.684648998</v>
       </c>
     </row>
@@ -2886,15 +2935,17 @@
       </c>
     </row>
     <row r="23" ht="28.8" customHeight="1" s="33">
-      <c r="A23" s="6" t="n">
-        <v>46284</v>
+      <c r="A23" s="37" t="n">
+        <v>46285</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>127.9</v>
+      </c>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="9">
         <f>IFERROR(C23/D23-1,"")</f>
@@ -2912,7 +2963,7 @@
       <c r="I23" s="9" t="n"/>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Not publicly reported</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3797,15 +3848,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n">
-        <v>46284</v>
+      <c r="A23" s="37" t="n">
+        <v>46285</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>129.83</v>
+      </c>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="9">
         <f>IFERROR(C23/D23-1,"")</f>
@@ -3823,7 +3876,7 @@
       <c r="I23" s="9" t="n"/>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Not publicly reported</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -4760,15 +4813,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n">
-        <v>46284</v>
+      <c r="A23" s="37" t="n">
+        <v>46285</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>130.01</v>
+      </c>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="9">
         <f>IFERROR(C23/D23-1,"")</f>
@@ -4790,7 +4845,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -5685,15 +5740,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n">
-        <v>46284</v>
+      <c r="A23" s="37" t="n">
+        <v>46285</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>133.72</v>
+      </c>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="9">
         <f>IFERROR(C23/D23-1,"")</f>
@@ -5711,7 +5768,7 @@
       <c r="I23" s="9" t="n"/>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Not publicly reported</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -6576,15 +6633,17 @@
       </c>
     </row>
     <row r="23" ht="28.8" customHeight="1" s="33">
-      <c r="A23" s="6" t="n">
-        <v>46284</v>
+      <c r="A23" s="37" t="n">
+        <v>46285</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>136.45</v>
+      </c>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="9">
         <f>IFERROR(C23/D23-1,"")</f>
@@ -6600,7 +6659,7 @@
       <c r="I23" s="9" t="n"/>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Not publicly reported</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">

--- a/Gold_ETF_Daily_Price_Tracker.xlsx
+++ b/Gold_ETF_Daily_Price_Tracker.xlsx
@@ -22,17 +22,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="dd\-mmm\-yy"/>
     <numFmt numFmtId="167" formatCode="[$₹-4009]#,##0.00"/>
     <numFmt numFmtId="168" formatCode="[$₹-4009]#,##0.00;[Red]\([$₹-4009]#,##0.00\)"/>
     <numFmt numFmtId="169" formatCode="0.00%;[Red]\(0.00%\)"/>
-    <numFmt numFmtId="170" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="171" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="172" formatCode="dd-mmm-yy"/>
-    <numFmt numFmtId="173" formatCode="[$₹-en-IN]#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="dd-mmm-yy"/>
+    <numFmt numFmtId="171" formatCode="[$₹-en-IN]#,##0.00"/>
+    <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -184,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -256,11 +255,18 @@
     <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -2134,40 +2140,40 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="n">
+      <c r="A11" s="38" t="n">
         <v>46285</v>
       </c>
-      <c r="B11" s="36" t="n">
+      <c r="B11" s="39" t="n">
         <v>127.9</v>
       </c>
-      <c r="C11" s="36" t="n">
+      <c r="C11" s="39" t="n">
         <v>301332.4</v>
       </c>
-      <c r="D11" s="36" t="n">
+      <c r="D11" s="39" t="n">
         <v>129.83</v>
       </c>
-      <c r="E11" s="36" t="n">
+      <c r="E11" s="39" t="n">
         <v>251091.22</v>
       </c>
-      <c r="F11" s="36" t="n">
+      <c r="F11" s="39" t="n">
         <v>130.01</v>
       </c>
-      <c r="G11" s="36" t="n">
+      <c r="G11" s="39" t="n">
         <v>200735.44</v>
       </c>
-      <c r="H11" s="36" t="n">
+      <c r="H11" s="39" t="n">
         <v>133.72</v>
       </c>
-      <c r="I11" s="36" t="n">
+      <c r="I11" s="39" t="n">
         <v>148562.92</v>
       </c>
-      <c r="J11" s="36" t="n">
+      <c r="J11" s="39" t="n">
         <v>136.45</v>
       </c>
-      <c r="K11" s="36" t="n">
+      <c r="K11" s="39" t="n">
         <v>100017.85</v>
       </c>
-      <c r="L11" s="36" t="n">
+      <c r="L11" s="39" t="n">
         <v>161432.684648998</v>
       </c>
     </row>
@@ -2935,7 +2941,7 @@
       </c>
     </row>
     <row r="23" ht="28.8" customHeight="1" s="33">
-      <c r="A23" s="37" t="n">
+      <c r="A23" s="40" t="n">
         <v>46285</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -3848,7 +3854,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="n">
+      <c r="A23" s="40" t="n">
         <v>46285</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -4813,7 +4819,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="n">
+      <c r="A23" s="40" t="n">
         <v>46285</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -5740,7 +5746,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="n">
+      <c r="A23" s="40" t="n">
         <v>46285</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -6633,7 +6639,7 @@
       </c>
     </row>
     <row r="23" ht="28.8" customHeight="1" s="33">
-      <c r="A23" s="37" t="n">
+      <c r="A23" s="40" t="n">
         <v>46285</v>
       </c>
       <c r="B23" s="7" t="inlineStr">

--- a/Gold_ETF_Daily_Price_Tracker.xlsx
+++ b/Gold_ETF_Daily_Price_Tracker.xlsx
@@ -2942,11 +2942,11 @@
     </row>
     <row r="23" ht="28.8" customHeight="1" s="33">
       <c r="A23" s="40" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -2985,11 +2985,11 @@
     </row>
     <row r="24" ht="28.8" customHeight="1" s="33">
       <c r="A24" s="6" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -3855,11 +3855,11 @@
     </row>
     <row r="23">
       <c r="A23" s="40" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -3898,11 +3898,11 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -4820,11 +4820,11 @@
     </row>
     <row r="23">
       <c r="A23" s="40" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -4867,11 +4867,11 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -5747,11 +5747,11 @@
     </row>
     <row r="23">
       <c r="A23" s="40" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -5790,11 +5790,11 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -6134,7 +6134,7 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>46272</v>
+        <v>46286</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
@@ -6640,11 +6640,11 @@
     </row>
     <row r="23" ht="28.8" customHeight="1" s="33">
       <c r="A23" s="40" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -6681,11 +6681,11 @@
     </row>
     <row r="24" ht="28.8" customHeight="1" s="33">
       <c r="A24" s="6" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>

--- a/Gold_ETF_Daily_Price_Tracker.xlsx
+++ b/Gold_ETF_Daily_Price_Tracker.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="dd\-mmm\-yy"/>
@@ -32,6 +32,7 @@
     <numFmt numFmtId="170" formatCode="dd-mmm-yy"/>
     <numFmt numFmtId="171" formatCode="[$₹-en-IN]#,##0.00"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="173" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -1728,7 +1729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="33" min="1" max="11"/>
@@ -2175,6 +2176,44 @@
       </c>
       <c r="L11" s="39" t="n">
         <v>161432.684648998</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="38" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B12" s="39" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="C12" s="39" t="n">
+        <v>301332.4</v>
+      </c>
+      <c r="D12" s="39" t="n">
+        <v>129.83</v>
+      </c>
+      <c r="E12" s="39" t="n">
+        <v>251091.22</v>
+      </c>
+      <c r="F12" s="39" t="n">
+        <v>130.01</v>
+      </c>
+      <c r="G12" s="39" t="n">
+        <v>200735.44</v>
+      </c>
+      <c r="H12" s="39" t="n">
+        <v>133.72</v>
+      </c>
+      <c r="I12" s="39" t="n">
+        <v>148562.92</v>
+      </c>
+      <c r="J12" s="39" t="n">
+        <v>137.1</v>
+      </c>
+      <c r="K12" s="39" t="n">
+        <v>100494.3</v>
+      </c>
+      <c r="L12" s="39" t="n">
+        <v>159856.409663393</v>
       </c>
     </row>
   </sheetData>

--- a/Gold_ETF_Daily_Price_Tracker.xlsx
+++ b/Gold_ETF_Daily_Price_Tracker.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="dd\-mmm\-yy"/>
@@ -32,7 +32,6 @@
     <numFmt numFmtId="170" formatCode="dd-mmm-yy"/>
     <numFmt numFmtId="171" formatCode="[$₹-en-IN]#,##0.00"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="173" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>

--- a/Gold_ETF_Daily_Price_Tracker.xlsx
+++ b/Gold_ETF_Daily_Price_Tracker.xlsx
@@ -183,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -267,6 +267,11 @@
     </xf>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1728,7 +1733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="33" min="1" max="11"/>
@@ -2141,7 +2146,7 @@
     </row>
     <row r="11">
       <c r="A11" s="38" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B11" s="39" t="n">
         <v>127.9</v>
@@ -2168,51 +2173,13 @@
         <v>148562.92</v>
       </c>
       <c r="J11" s="39" t="n">
-        <v>136.45</v>
+        <v>137.1</v>
       </c>
       <c r="K11" s="39" t="n">
-        <v>100017.85</v>
+        <v>100494.3</v>
       </c>
       <c r="L11" s="39" t="n">
-        <v>161432.684648998</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="38" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B12" s="39" t="n">
-        <v>127.9</v>
-      </c>
-      <c r="C12" s="39" t="n">
-        <v>301332.4</v>
-      </c>
-      <c r="D12" s="39" t="n">
-        <v>129.83</v>
-      </c>
-      <c r="E12" s="39" t="n">
-        <v>251091.22</v>
-      </c>
-      <c r="F12" s="39" t="n">
-        <v>130.01</v>
-      </c>
-      <c r="G12" s="39" t="n">
-        <v>200735.44</v>
-      </c>
-      <c r="H12" s="39" t="n">
-        <v>133.72</v>
-      </c>
-      <c r="I12" s="39" t="n">
-        <v>148562.92</v>
-      </c>
-      <c r="J12" s="39" t="n">
-        <v>137.1</v>
-      </c>
-      <c r="K12" s="39" t="n">
-        <v>100494.3</v>
-      </c>
-      <c r="L12" s="39" t="n">
-        <v>159856.409663393</v>
+        <v>160141.0003503818</v>
       </c>
     </row>
   </sheetData>
@@ -2271,7 +2238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="15" customWidth="1" style="33" min="1" max="1"/>
@@ -2990,7 +2957,9 @@
       <c r="C23" s="8" t="n">
         <v>127.9</v>
       </c>
-      <c r="D23" s="8" t="n"/>
+      <c r="D23" s="43" t="n">
+        <v>129.4092</v>
+      </c>
       <c r="E23" s="9">
         <f>IFERROR(C23/D23-1,"")</f>
         <v/>
@@ -3021,145 +2990,61 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="28.8" customHeight="1" s="33">
-      <c r="A24" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="9">
-        <f>IFERROR(C24/D24-1,"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>0.0059</v>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly reported</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>No price observation retrieved</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>No NAV observation in supplied extract</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28.8" customHeight="1" s="33">
-      <c r="A25" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="9">
-        <f>IFERROR(C25/D25-1,"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>0.0059</v>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly reported</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>No price observation retrieved</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>No NAV observation in supplied extract</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
+    <row r="24" ht="28.8" customHeight="1" s="33"/>
+    <row r="25" ht="28.8" customHeight="1" s="33"/>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>NAV source</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>User-supplied UTI Mutual Fund / AMFI NAV extract; official history endpoint: https://portal.amfiindia.com/DownloadNAVHistoryReport_Po.aspx?frmdt=07-Sep-2026&amp;todt=21-Sep-2026</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="31" t="inlineStr">
-        <is>
-          <t>Sources</t>
-        </is>
-      </c>
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>TER source</t>
+        </is>
+      </c>
+      <c r="B28" s="29" t="n"/>
     </row>
     <row r="29" ht="144" customHeight="1" s="33">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>NAV source</t>
+          <t>TD source</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>User-supplied UTI Mutual Fund / AMFI NAV extract; official history endpoint: https://portal.amfiindia.com/DownloadNAVHistoryReport_Po.aspx?frmdt=07-Sep-2026&amp;todt=21-Sep-2026</t>
+          <t>https://www.utimf.com/mutual-funds/uti-gold-exchange-traded-fund</t>
         </is>
       </c>
     </row>
     <row r="30" ht="57.6" customHeight="1" s="33">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>TER source</t>
+          <t>Market-price source</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>https://www.dezerv.in/mutual-funds/uti-gold-etf-inf789f1aux7/</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="72" customHeight="1" s="33">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>TD source</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>https://www.utimf.com/mutual-funds/uti-gold-exchange-traded-fund</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="43.2" customHeight="1" s="33">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Market-price source</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
           <t>https://finance.yahoo.com/quote/GOLDBETA.NS/history/</t>
         </is>
       </c>
     </row>
+    <row r="31" ht="72" customHeight="1" s="33"/>
+    <row r="32" ht="43.2" customHeight="1" s="33"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="E3:L8"/>
@@ -3188,7 +3073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="15" customWidth="1" style="33" min="1" max="1"/>
@@ -3903,7 +3788,9 @@
       <c r="C23" s="8" t="n">
         <v>129.83</v>
       </c>
-      <c r="D23" s="8" t="n"/>
+      <c r="D23" s="43" t="n">
+        <v>129.6745</v>
+      </c>
       <c r="E23" s="9">
         <f>IFERROR(C23/D23-1,"")</f>
         <v/>
@@ -3934,145 +3821,61 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="9">
-        <f>IFERROR(C24/D24-1,"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly reported</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>No price observation retrieved</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>Not available for this date</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="9">
-        <f>IFERROR(C25/D25-1,"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly reported</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>No price observation retrieved</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>Not available for this date</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>NAV source</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>User-supplied HDFC Mutual Fund / AMFI NAV extract (HDFC Gold ETF - Growth Option); daily values verified for 07-Sep-2026 to 18-Sep-2026.</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="31" t="inlineStr">
-        <is>
-          <t>Sources</t>
-        </is>
-      </c>
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>TER source</t>
+        </is>
+      </c>
+      <c r="B28" s="29" t="n"/>
     </row>
     <row r="29" ht="115.2" customHeight="1" s="33">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>NAV source</t>
+          <t>TD source</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>User-supplied HDFC Mutual Fund / AMFI NAV extract (HDFC Gold ETF - Growth Option); daily values verified for 07-Sep-2026 to 18-Sep-2026.</t>
+          <t>https://www.hdfcfund.com/explore/mutual-funds/hdfc-gold-etf/regular</t>
         </is>
       </c>
     </row>
     <row r="30" ht="72" customHeight="1" s="33">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>TER source</t>
+          <t>Market-price source</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>https://www.advisorkhoj.com/mutual-funds-research/HDFC-Gold-ETF-Growth-Option</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="57.6" customHeight="1" s="33">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>TD source</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>https://www.hdfcfund.com/explore/mutual-funds/hdfc-gold-etf/regular</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="43.2" customHeight="1" s="33">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Market-price source</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
           <t>https://finance.yahoo.com/quote/HDFCGOLD.NS/history/</t>
         </is>
       </c>
     </row>
+    <row r="31" ht="57.6" customHeight="1" s="33"/>
+    <row r="32" ht="43.2" customHeight="1" s="33"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="E3:L8"/>
@@ -4101,7 +3904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="15" customWidth="1" style="33" min="1" max="1"/>
@@ -4868,7 +4671,9 @@
       <c r="C23" s="8" t="n">
         <v>130.01</v>
       </c>
-      <c r="D23" s="8" t="n"/>
+      <c r="D23" s="43" t="n">
+        <v>127.749</v>
+      </c>
       <c r="E23" s="9">
         <f>IFERROR(C23/D23-1,"")</f>
         <v/>
@@ -4903,153 +4708,61 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="9">
-        <f>IFERROR(C24/D24-1,"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>-0.0165</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>-0.0137</v>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>No price observation retrieved</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>Not available for this date</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="9">
-        <f>IFERROR(C25/D25-1,"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="n">
-        <v>-0.0165</v>
-      </c>
-      <c r="I25" s="9" t="n">
-        <v>-0.0137</v>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>No price observation retrieved</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>Not available for this date</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>NAV source</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>User-supplied ICICI Prudential Mutual Fund NAV extract (ICICI Prudential Gold ETF); daily values verified for 07-Sep-2026 to 18-Sep-2026.</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="31" t="inlineStr">
-        <is>
-          <t>Sources</t>
-        </is>
-      </c>
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>TER source</t>
+        </is>
+      </c>
+      <c r="B28" s="29" t="n"/>
     </row>
     <row r="29" ht="115.2" customHeight="1" s="33">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>NAV source</t>
+          <t>TD source</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>User-supplied ICICI Prudential Mutual Fund NAV extract (ICICI Prudential Gold ETF); daily values verified for 07-Sep-2026 to 18-Sep-2026.</t>
+          <t>https://www.icicipruamc.com/blob/knowledgecentre/factsheet-passive/Passive.pdf</t>
         </is>
       </c>
     </row>
     <row r="30" ht="72" customHeight="1" s="33">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>TER source</t>
+          <t>Market-price source</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>https://www.icicipruamc.com/blob/knowledgecentre/factsheet-passive/Passive.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="72" customHeight="1" s="33">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>TD source</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>https://www.icicipruamc.com/blob/knowledgecentre/factsheet-passive/Passive.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="43.2" customHeight="1" s="33">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Market-price source</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
           <t>https://finance.yahoo.com/quote/GOLDIETF.NS/history/</t>
         </is>
       </c>
     </row>
+    <row r="31" ht="72" customHeight="1" s="33"/>
+    <row r="32" ht="43.2" customHeight="1" s="33"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="E3:L8"/>
@@ -5078,7 +4791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="15" customWidth="1" style="33" min="1" max="1"/>
@@ -5795,7 +5508,9 @@
       <c r="C23" s="8" t="n">
         <v>133.72</v>
       </c>
-      <c r="D23" s="8" t="n"/>
+      <c r="D23" s="43" t="n">
+        <v>133.5272</v>
+      </c>
       <c r="E23" s="9">
         <f>IFERROR(C23/D23-1,"")</f>
         <v/>
@@ -5826,145 +5541,61 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="9">
-        <f>IFERROR(C24/D24-1,"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly reported</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>No price observation retrieved</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>Not available for this date</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="9">
-        <f>IFERROR(C25/D25-1,"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly reported</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>No price observation retrieved</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>Not available for this date</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>NAV source</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>https://portal.amfiindia.com/DownloadNAVHistoryReport_Po.aspx?frmdt=07-Sep-2026&amp;todt=21-Sep-2026</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="31" t="inlineStr">
-        <is>
-          <t>Sources</t>
-        </is>
-      </c>
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>TER source</t>
+        </is>
+      </c>
+      <c r="B28" s="29" t="n"/>
     </row>
     <row r="29" ht="86.40000000000001" customHeight="1" s="33">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>NAV source</t>
+          <t>TD source</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>https://portal.amfiindia.com/DownloadNAVHistoryReport_Po.aspx?frmdt=07-Sep-2026&amp;todt=21-Sep-2026</t>
+          <t>https://www.amfiindia.com/otherdata/tracking-error</t>
         </is>
       </c>
     </row>
     <row r="30" ht="57.6" customHeight="1" s="33">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>TER source</t>
+          <t>Market-price source</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>https://mutualfund.adityabirlacapital.com/empower/Passive-ETFs/Gold-ETF.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="43.2" customHeight="1" s="33">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>TD source</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>https://www.amfiindia.com/otherdata/tracking-error</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="43.2" customHeight="1" s="33">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Market-price source</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
           <t>https://finance.yahoo.com/quote/BSLGOLDETF.NS/history/</t>
         </is>
       </c>
     </row>
+    <row r="31" ht="43.2" customHeight="1" s="33"/>
+    <row r="32" ht="43.2" customHeight="1" s="33"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="E3:L8"/>
@@ -5993,7 +5624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="15" customWidth="1" style="33" min="1" max="1"/>
@@ -6677,181 +6308,81 @@
       </c>
     </row>
     <row r="23" ht="28.8" customHeight="1" s="33">
-      <c r="A23" s="40" t="n">
+      <c r="A23" s="42" t="n">
         <v>46286</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" t="n">
         <v>136.45</v>
       </c>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="9">
-        <f>IFERROR(C23/D23-1,"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Not reliably reported</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>No price observation retrieved</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>No NAV observation in supplied extract</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28.8" customHeight="1" s="33">
-      <c r="A24" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="9">
-        <f>IFERROR(C24/D24-1,"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Not reliably reported</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly reported</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>No price observation retrieved</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>No NAV observation in supplied extract</t>
-        </is>
-      </c>
-    </row>
+      <c r="D23" s="39" t="n">
+        <v>136.7891</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28.8" customHeight="1" s="33"/>
     <row r="25" ht="28.8" customHeight="1" s="33">
-      <c r="A25" s="6" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="9">
-        <f>IFERROR(C25/D25-1,"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Not reliably reported</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>Not publicly reported</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>No price observation retrieved</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>No NAV observation in supplied extract</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>NAV source</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>User-supplied LIC Mutual Fund NAV extract (LIC MF Gold Exchange Traded Fund); daily values verified for 07-Sep-2026 to 18-Sep-2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>TER source</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>https://www.licmf.com/snapshot/licmf-gold-exchange-traded-fund/LIC193</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="31" t="inlineStr">
-        <is>
-          <t>Sources</t>
-        </is>
-      </c>
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>TD source</t>
+        </is>
+      </c>
+      <c r="B28" s="29" t="n"/>
     </row>
     <row r="29" ht="115.2" customHeight="1" s="33">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>NAV source</t>
+          <t>Market-price source</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>User-supplied LIC Mutual Fund NAV extract (LIC MF Gold Exchange Traded Fund); daily values verified for 07-Sep-2026 to 18-Sep-2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="57.6" customHeight="1" s="33">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>TER source</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>https://www.licmf.com/snapshot/licmf-gold-exchange-traded-fund/LIC193</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="72" customHeight="1" s="33">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>TD source</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>https://www.licmf.com/assets/downloads/sai_sid_kim/2025-2026/39-856338300.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="43.2" customHeight="1" s="33">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Market-price source</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
           <t>https://finance.yahoo.com/quote/LICMFGOLD.NS/history/</t>
         </is>
       </c>
     </row>
+    <row r="30" ht="57.6" customHeight="1" s="33"/>
+    <row r="31" ht="72" customHeight="1" s="33"/>
+    <row r="32" ht="43.2" customHeight="1" s="33"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="E3:L8"/>

--- a/Gold_ETF_Daily_Price_Tracker.xlsx
+++ b/Gold_ETF_Daily_Price_Tracker.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="dd\-mmm\-yy"/>
@@ -32,6 +32,7 @@
     <numFmt numFmtId="170" formatCode="dd-mmm-yy"/>
     <numFmt numFmtId="171" formatCode="[$₹-en-IN]#,##0.00"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="173" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -1733,7 +1734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="33" min="1" max="11"/>
@@ -2180,6 +2181,44 @@
       </c>
       <c r="L11" s="39" t="n">
         <v>160141.0003503818</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="38" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B12" s="39" t="n">
+        <v>127.25</v>
+      </c>
+      <c r="C12" s="39" t="n">
+        <v>299801</v>
+      </c>
+      <c r="D12" s="39" t="n">
+        <v>129.26</v>
+      </c>
+      <c r="E12" s="39" t="n">
+        <v>249988.84</v>
+      </c>
+      <c r="F12" s="39" t="n">
+        <v>129.42</v>
+      </c>
+      <c r="G12" s="39" t="n">
+        <v>199824.48</v>
+      </c>
+      <c r="H12" s="39" t="n">
+        <v>133.06</v>
+      </c>
+      <c r="I12" s="39" t="n">
+        <v>147829.66</v>
+      </c>
+      <c r="J12" s="39" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="K12" s="39" t="n">
+        <v>99541.40000000001</v>
+      </c>
+      <c r="L12" s="39" t="n">
+        <v>159370.7392300716</v>
       </c>
     </row>
   </sheetData>
@@ -2990,7 +3029,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="28.8" customHeight="1" s="33"/>
+    <row r="24" ht="28.8" customHeight="1" s="33">
+      <c r="A24" s="42" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>127.25</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
     <row r="25" ht="28.8" customHeight="1" s="33"/>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
@@ -3821,7 +3877,24 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
+    <row r="24">
+      <c r="A24" s="42" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>129.26</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
     <row r="25"/>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
@@ -4708,7 +4781,24 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
+    <row r="24">
+      <c r="A24" s="42" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>129.42</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
     <row r="25"/>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
@@ -5541,7 +5631,24 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
+    <row r="24">
+      <c r="A24" s="42" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>133.06</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
     <row r="25"/>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
@@ -6328,7 +6435,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="28.8" customHeight="1" s="33"/>
+    <row r="24" ht="28.8" customHeight="1" s="33">
+      <c r="A24" s="42" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
     <row r="25" ht="28.8" customHeight="1" s="33">
       <c r="A25" s="31" t="inlineStr">
         <is>

--- a/Gold_ETF_Daily_Price_Tracker.xlsx
+++ b/Gold_ETF_Daily_Price_Tracker.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="dd\-mmm\-yy"/>
@@ -32,7 +32,6 @@
     <numFmt numFmtId="170" formatCode="dd-mmm-yy"/>
     <numFmt numFmtId="171" formatCode="[$₹-en-IN]#,##0.00"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="173" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -6447,6 +6446,9 @@
       <c r="C24" t="n">
         <v>135.8</v>
       </c>
+      <c r="D24" s="39" t="n">
+        <v>136.1354</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Available</t>

--- a/Gold_ETF_Daily_Price_Tracker.xlsx
+++ b/Gold_ETF_Daily_Price_Tracker.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="dd\-mmm\-yy"/>
@@ -32,6 +32,7 @@
     <numFmt numFmtId="170" formatCode="dd-mmm-yy"/>
     <numFmt numFmtId="171" formatCode="[$₹-en-IN]#,##0.00"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="173" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -183,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -274,6 +275,7 @@
     <xf numFmtId="171" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="172" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1733,7 +1735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="33" min="1" max="11"/>
@@ -2218,6 +2220,44 @@
       </c>
       <c r="L12" s="39" t="n">
         <v>159370.7392300716</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B13" s="39" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="C13" s="39" t="n">
+        <v>299447.6</v>
+      </c>
+      <c r="D13" s="39" t="n">
+        <v>128.94</v>
+      </c>
+      <c r="E13" s="39" t="n">
+        <v>249369.96</v>
+      </c>
+      <c r="F13" s="39" t="n">
+        <v>129.21</v>
+      </c>
+      <c r="G13" s="39" t="n">
+        <v>199500.24</v>
+      </c>
+      <c r="H13" s="39" t="n">
+        <v>132.9</v>
+      </c>
+      <c r="I13" s="39" t="n">
+        <v>147651.9</v>
+      </c>
+      <c r="J13" s="39" t="n">
+        <v>135.9</v>
+      </c>
+      <c r="K13" s="39" t="n">
+        <v>99614.7</v>
+      </c>
+      <c r="L13" s="39" t="n">
+        <v>158230.1488120125</v>
       </c>
     </row>
   </sheetData>
@@ -3040,13 +3080,33 @@
       <c r="C24" t="n">
         <v>127.25</v>
       </c>
+      <c r="D24" s="39" t="n">
+        <v>128.7893</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28.8" customHeight="1" s="33"/>
+    <row r="25" ht="28.8" customHeight="1" s="33">
+      <c r="A25" s="42" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
         <is>
@@ -3888,13 +3948,33 @@
       <c r="C24" t="n">
         <v>129.26</v>
       </c>
+      <c r="D24" s="39" t="n">
+        <v>129.0517</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
+    <row r="25">
+      <c r="A25" s="42" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>128.94</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
         <is>
@@ -4792,13 +4872,33 @@
       <c r="C24" t="n">
         <v>129.42</v>
       </c>
+      <c r="D24" s="39" t="n">
+        <v>127.1338</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
+    <row r="25">
+      <c r="A25" s="42" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>129.21</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
         <is>
@@ -5642,13 +5742,33 @@
       <c r="C24" t="n">
         <v>133.06</v>
       </c>
+      <c r="D24" s="39" t="n">
+        <v>132.8879</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
+    <row r="25">
+      <c r="A25" s="42" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>132.9</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
         <is>
@@ -6456,9 +6576,20 @@
       </c>
     </row>
     <row r="25" ht="28.8" customHeight="1" s="33">
-      <c r="A25" s="31" t="inlineStr">
-        <is>
-          <t>Sources</t>
+      <c r="A25" s="44" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>135.9</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>

--- a/Gold_ETF_Daily_Price_Tracker.xlsx
+++ b/Gold_ETF_Daily_Price_Tracker.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="dd\-mmm\-yy"/>
@@ -32,7 +32,6 @@
     <numFmt numFmtId="170" formatCode="dd-mmm-yy"/>
     <numFmt numFmtId="171" formatCode="[$₹-en-IN]#,##0.00"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="173" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -5763,6 +5762,9 @@
       <c r="C25" t="n">
         <v>132.9</v>
       </c>
+      <c r="D25" s="39" t="n">
+        <v>132.487</v>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Available</t>
@@ -6587,6 +6589,9 @@
       <c r="C25" t="n">
         <v>135.9</v>
       </c>
+      <c r="D25" s="39" t="n">
+        <v>135.7255</v>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Available</t>

--- a/Gold_ETF_Daily_Price_Tracker.xlsx
+++ b/Gold_ETF_Daily_Price_Tracker.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="dd\-mmm\-yy"/>
@@ -32,6 +32,7 @@
     <numFmt numFmtId="170" formatCode="dd-mmm-yy"/>
     <numFmt numFmtId="171" formatCode="[$₹-en-IN]#,##0.00"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="173" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -183,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -275,6 +276,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="172" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1734,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="33" min="1" max="11"/>
@@ -2257,6 +2259,44 @@
       </c>
       <c r="L13" s="39" t="n">
         <v>158230.1488120125</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="38" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B14" s="39" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="C14" s="39" t="n">
+        <v>296384.8</v>
+      </c>
+      <c r="D14" s="39" t="n">
+        <v>127.64</v>
+      </c>
+      <c r="E14" s="39" t="n">
+        <v>246855.76</v>
+      </c>
+      <c r="F14" s="39" t="n">
+        <v>127.88</v>
+      </c>
+      <c r="G14" s="39" t="n">
+        <v>197446.72</v>
+      </c>
+      <c r="H14" s="39" t="n">
+        <v>131.48</v>
+      </c>
+      <c r="I14" s="39" t="n">
+        <v>146074.28</v>
+      </c>
+      <c r="J14" s="39" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="K14" s="39" t="n">
+        <v>98588.5</v>
+      </c>
+      <c r="L14" s="39" t="n">
+        <v>157213.399658606</v>
       </c>
     </row>
   </sheetData>
@@ -3100,6 +3140,9 @@
       <c r="C25" t="n">
         <v>127.1</v>
       </c>
+      <c r="D25" s="39" t="n">
+        <v>128.4002</v>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Available</t>
@@ -3107,9 +3150,20 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>Sources</t>
+      <c r="A26" s="44" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3968,6 +4022,9 @@
       <c r="C25" t="n">
         <v>128.94</v>
       </c>
+      <c r="D25" s="39" t="n">
+        <v>128.661</v>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Available</t>
@@ -3975,9 +4032,20 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>Sources</t>
+      <c r="A26" s="44" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>127.64</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4892,6 +4960,9 @@
       <c r="C25" t="n">
         <v>129.21</v>
       </c>
+      <c r="D25" s="39" t="n">
+        <v>126.7478</v>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Available</t>
@@ -4899,9 +4970,20 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>Sources</t>
+      <c r="A26" s="44" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>127.88</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -5772,9 +5854,20 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>Sources</t>
+      <c r="A26" s="44" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>131.48</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -6599,14 +6692,20 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>NAV source</t>
-        </is>
+      <c r="A26" s="45" t="n">
+        <v>46289</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>User-supplied LIC Mutual Fund NAV extract (LIC MF Gold Exchange Traded Fund); daily values verified for 07-Sep-2026 to 18-Sep-2026.</t>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>

--- a/Gold_ETF_Daily_Price_Tracker.xlsx
+++ b/Gold_ETF_Daily_Price_Tracker.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="dd\-mmm\-yy"/>
@@ -32,7 +32,6 @@
     <numFmt numFmtId="170" formatCode="dd-mmm-yy"/>
     <numFmt numFmtId="171" formatCode="[$₹-en-IN]#,##0.00"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="173" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -3161,6 +3160,9 @@
       <c r="C26" t="n">
         <v>125.8</v>
       </c>
+      <c r="D26" s="39" t="n">
+        <v>127.3068</v>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Available</t>
@@ -4043,6 +4045,9 @@
       <c r="C26" t="n">
         <v>127.64</v>
       </c>
+      <c r="D26" s="39" t="n">
+        <v>127.5625</v>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Available</t>
@@ -6703,6 +6708,9 @@
       <c r="C26" t="n">
         <v>134.5</v>
       </c>
+      <c r="D26" s="39" t="n">
+        <v>134.5721</v>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Available</t>

--- a/Gold_ETF_Daily_Price_Tracker.xlsx
+++ b/Gold_ETF_Daily_Price_Tracker.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="dd\-mmm\-yy"/>
@@ -32,6 +32,7 @@
     <numFmt numFmtId="170" formatCode="dd-mmm-yy"/>
     <numFmt numFmtId="171" formatCode="[$₹-en-IN]#,##0.00"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="173" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -1735,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18" customWidth="1" style="33" min="1" max="11"/>
@@ -2296,6 +2297,44 @@
       </c>
       <c r="L14" s="39" t="n">
         <v>157213.399658606</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="38" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B15" s="39" t="n">
+        <v>126.65</v>
+      </c>
+      <c r="C15" s="39" t="n">
+        <v>298387.4</v>
+      </c>
+      <c r="D15" s="39" t="n">
+        <v>128.63</v>
+      </c>
+      <c r="E15" s="39" t="n">
+        <v>248770.42</v>
+      </c>
+      <c r="F15" s="39" t="n">
+        <v>129.03</v>
+      </c>
+      <c r="G15" s="39" t="n">
+        <v>199222.32</v>
+      </c>
+      <c r="H15" s="39" t="n">
+        <v>132.4</v>
+      </c>
+      <c r="I15" s="39" t="n">
+        <v>147096.4</v>
+      </c>
+      <c r="J15" s="39" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="K15" s="39" t="n">
+        <v>99468.09999999999</v>
+      </c>
+      <c r="L15" s="39" t="n">
+        <v>158193.0829504164</v>
       </c>
     </row>
   </sheetData>
@@ -3170,14 +3209,20 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>NAV source</t>
-        </is>
+      <c r="A27" s="45" t="n">
+        <v>46290</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>User-supplied UTI Mutual Fund / AMFI NAV extract; official history endpoint: https://portal.amfiindia.com/DownloadNAVHistoryReport_Po.aspx?frmdt=07-Sep-2026&amp;todt=21-Sep-2026</t>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>126.65</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4055,14 +4100,20 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>NAV source</t>
-        </is>
+      <c r="A27" s="45" t="n">
+        <v>46290</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>User-supplied HDFC Mutual Fund / AMFI NAV extract (HDFC Gold ETF - Growth Option); daily values verified for 07-Sep-2026 to 18-Sep-2026.</t>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>128.63</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4986,6 +5037,9 @@
       <c r="C26" t="n">
         <v>127.88</v>
       </c>
+      <c r="D26" s="39" t="n">
+        <v>125.6627</v>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Available</t>
@@ -4993,14 +5047,20 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>NAV source</t>
-        </is>
+      <c r="A27" s="45" t="n">
+        <v>46290</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>User-supplied ICICI Prudential Mutual Fund NAV extract (ICICI Prudential Gold ETF); daily values verified for 07-Sep-2026 to 18-Sep-2026.</t>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>129.03</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -5870,6 +5930,9 @@
       <c r="C26" t="n">
         <v>131.48</v>
       </c>
+      <c r="D26" s="39" t="n">
+        <v>131.3591</v>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Available</t>
@@ -5877,14 +5940,20 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>NAV source</t>
-        </is>
+      <c r="A27" s="45" t="n">
+        <v>46290</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>https://portal.amfiindia.com/DownloadNAVHistoryReport_Po.aspx?frmdt=07-Sep-2026&amp;todt=21-Sep-2026</t>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>132.4</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -6718,14 +6787,20 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>TER source</t>
-        </is>
+      <c r="A27" s="45" t="n">
+        <v>46290</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>https://www.licmf.com/snapshot/licmf-gold-exchange-traded-fund/LIC193</t>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>

--- a/Gold_ETF_Daily_Price_Tracker.xlsx
+++ b/Gold_ETF_Daily_Price_Tracker.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="dd\-mmm\-yy"/>
@@ -32,7 +32,6 @@
     <numFmt numFmtId="170" formatCode="dd-mmm-yy"/>
     <numFmt numFmtId="171" formatCode="[$₹-en-IN]#,##0.00"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="173" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -3220,6 +3219,9 @@
       <c r="C27" t="n">
         <v>126.65</v>
       </c>
+      <c r="D27" s="39" t="n">
+        <v>128.3633</v>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Available</t>
@@ -4111,6 +4113,9 @@
       <c r="C27" t="n">
         <v>128.63</v>
       </c>
+      <c r="D27" s="39" t="n">
+        <v>128.625</v>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Available</t>
@@ -5058,6 +5063,9 @@
       <c r="C27" t="n">
         <v>129.03</v>
       </c>
+      <c r="D27" s="39" t="n">
+        <v>126.7123</v>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Available</t>
@@ -5951,6 +5959,9 @@
       <c r="C27" t="n">
         <v>132.4</v>
       </c>
+      <c r="D27" s="39" t="n">
+        <v>132.4512</v>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Available</t>
@@ -6798,6 +6809,9 @@
       <c r="C27" t="n">
         <v>135.7</v>
       </c>
+      <c r="D27" s="39" t="n">
+        <v>135.6887</v>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Available</t>
